--- a/data/trans_orig/P2A_senso_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_senso_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2007</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8208</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3766</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15491</t>
+          <t>15416</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485631</t>
+          <t>485856</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>455662</t>
+          <t>455042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>465512</t>
+          <t>464788</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>946062</t>
+          <t>946137</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>957748</t>
+          <t>957787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13006</t>
+          <t>13182</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1885</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17680</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>722483</t>
+          <t>722307</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>733596</t>
+          <t>733608</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>614064</t>
+          <t>614671</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>623546</t>
+          <t>623609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1343302</t>
+          <t>1342362</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1355707</t>
+          <t>1355572</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12959</t>
+          <t>13813</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>12920</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>20606</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>625709</t>
+          <t>624855</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>636998</t>
+          <t>637640</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>676828</t>
+          <t>676824</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>687599</t>
+          <t>687566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1306764</t>
+          <t>1307806</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1322701</t>
+          <t>1322743</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12680</t>
+          <t>12621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19660</t>
+          <t>17770</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9041</t>
+          <t>9422</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26504</t>
+          <t>26498</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>506467</t>
+          <t>506526</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>517063</t>
+          <t>517062</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>495982</t>
+          <t>497872</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>510310</t>
+          <t>510504</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1008285</t>
+          <t>1008291</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1025748</t>
+          <t>1025367</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7559</t>
+          <t>7182</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21883</t>
+          <t>21273</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16305</t>
+          <t>16256</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13677</t>
+          <t>13052</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30920</t>
+          <t>31532</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>364827</t>
+          <t>365437</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>379151</t>
+          <t>379528</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>387681</t>
+          <t>387730</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>400145</t>
+          <t>399805</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>759776</t>
+          <t>759164</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>777019</t>
+          <t>777644</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7778</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>21313</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12152</t>
+          <t>12531</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28141</t>
+          <t>29102</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271176</t>
+          <t>271270</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284805</t>
+          <t>284640</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>331030</t>
+          <t>331861</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>340234</t>
+          <t>341038</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>607376</t>
+          <t>606415</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>623365</t>
+          <t>622986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1799</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>11729</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24773</t>
+          <t>23551</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29690</t>
+          <t>30249</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>198280</t>
+          <t>198154</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>208105</t>
+          <t>208084</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>309135</t>
+          <t>310357</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>324981</t>
+          <t>326089</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>514101</t>
+          <t>513542</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>532153</t>
+          <t>531741</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38003</t>
+          <t>37661</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66259</t>
+          <t>66661</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42733</t>
+          <t>43136</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73473</t>
+          <t>72447</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>86200</t>
+          <t>87814</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>127504</t>
+          <t>127417</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3210284</t>
+          <t>3209882</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3238540</t>
+          <t>3238882</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3305724</t>
+          <t>3306750</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3336464</t>
+          <t>3336061</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6528237</t>
+          <t>6528324</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6569541</t>
+          <t>6567927</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2012</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12225</t>
+          <t>12549</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14927</t>
+          <t>15183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>441921</t>
+          <t>441597</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452065</t>
+          <t>452040</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>423940</t>
+          <t>423572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>869449</t>
+          <t>869193</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>880417</t>
+          <t>880420</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10526</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8147</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25212</t>
+          <t>24119</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>11190</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30688</t>
+          <t>30216</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>676561</t>
+          <t>677062</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>685270</t>
+          <t>685291</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>585043</t>
+          <t>586136</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>602108</t>
+          <t>602714</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1266654</t>
+          <t>1267126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1285606</t>
+          <t>1286152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2929</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14625</t>
+          <t>16461</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21753</t>
+          <t>20300</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,47 +4448,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>18849</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>11395</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>30905</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>18849</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>10932</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>29493</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667238</t>
+          <t>665402</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678978</t>
+          <t>678934</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>689097</t>
+          <t>690550</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>705045</t>
+          <t>704964</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,47 +4561,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>99,17%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1373863</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1361807</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1381317</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>97,78%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>99,18%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1373863</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1363219</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>1381780</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25690</t>
+          <t>26384</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25295</t>
+          <t>24428</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20216</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43838</t>
+          <t>44461</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>588927</t>
+          <t>588233</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>606964</t>
+          <t>607105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>590904</t>
+          <t>591771</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>607854</t>
+          <t>607966</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1186978</t>
+          <t>1186355</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1210600</t>
+          <t>1211531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4070</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15825</t>
+          <t>15815</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20594</t>
+          <t>19712</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12587</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30220</t>
+          <t>31121</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>413604</t>
+          <t>413614</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>425299</t>
+          <t>425359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>427206</t>
+          <t>428088</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>441426</t>
+          <t>441521</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>847009</t>
+          <t>846108</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>864642</t>
+          <t>864377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14068</t>
+          <t>15078</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20070</t>
+          <t>19257</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>10055</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28874</t>
+          <t>27958</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>295718</t>
+          <t>294708</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>307894</t>
+          <t>307768</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>333926</t>
+          <t>334739</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>347874</t>
+          <t>348239</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>634908</t>
+          <t>635824</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>653675</t>
+          <t>653727</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18487</t>
+          <t>18061</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>6247</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>19793</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>13670</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33984</t>
+          <t>32584</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>231364</t>
+          <t>231790</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244470</t>
+          <t>244786</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>368917</t>
+          <t>369186</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>382753</t>
+          <t>382732</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>604846</t>
+          <t>606246</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>624503</t>
+          <t>625160</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43387</t>
+          <t>43454</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>75044</t>
+          <t>76525</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,34 +6133,34 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>77898</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>62695</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>97628</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
           <t>2,19%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>77898</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>62677</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>98308</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
           <t>1,76%</t>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>112471</t>
+          <t>113441</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>161895</t>
+          <t>160581</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3351735</t>
+          <t>3350254</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3383392</t>
+          <t>3383325</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,42 +6241,42 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3480411</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3460681</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3495614</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
           <t>97,81%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>3227</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3480411</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3460001</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3495632</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6823193</t>
+          <t>6824507</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6872617</t>
+          <t>6871647</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,38%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2016</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4485</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414434</t>
+          <t>414581</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>391270</t>
+          <t>391283</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>808607</t>
+          <t>809372</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10290</t>
+          <t>9872</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13430</t>
+          <t>13290</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>583087</t>
+          <t>583716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>553254</t>
+          <t>553672</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561720</t>
+          <t>561891</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1140610</t>
+          <t>1140750</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1151212</t>
+          <t>1151139</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12370</t>
+          <t>12585</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9555</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>4888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18699</t>
+          <t>17990</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656727</t>
+          <t>656512</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667156</t>
+          <t>667165</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>651831</t>
+          <t>651001</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>659541</t>
+          <t>659527</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1311784</t>
+          <t>1312493</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1325348</t>
+          <t>1325595</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21440</t>
+          <t>22658</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>12869</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10669</t>
+          <t>11025</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28785</t>
+          <t>28819</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>624608</t>
+          <t>623390</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639115</t>
+          <t>639616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>635016</t>
+          <t>636208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>646089</t>
+          <t>647042</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1266340</t>
+          <t>1266306</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1284456</t>
+          <t>1284100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14246</t>
+          <t>14876</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9673</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18221</t>
+          <t>19081</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463672</t>
+          <t>463042</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476212</t>
+          <t>475979</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>487176</t>
+          <t>487621</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>495881</t>
+          <t>495883</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>956546</t>
+          <t>955686</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>970646</t>
+          <t>970661</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>11375</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18064</t>
+          <t>18217</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323611</t>
+          <t>323968</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>333395</t>
+          <t>333381</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>365881</t>
+          <t>366387</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>375742</t>
+          <t>375727</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>694028</t>
+          <t>693875</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>707309</t>
+          <t>707312</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>808</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9430</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23095</t>
+          <t>22520</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26617</t>
+          <t>28244</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>247568</t>
+          <t>247672</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>256083</t>
+          <t>256190</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>377074</t>
+          <t>377649</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>393935</t>
+          <t>394162</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>630550</t>
+          <t>628923</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>648887</t>
+          <t>648167</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,63%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23416</t>
+          <t>22996</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>50009</t>
+          <t>48808</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27272</t>
+          <t>26546</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>52016</t>
+          <t>51329</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54633</t>
+          <t>56035</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>90956</t>
+          <t>93225</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3344341</t>
+          <t>3345542</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3370934</t>
+          <t>3371354</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3492526</t>
+          <t>3493213</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3517270</t>
+          <t>3517996</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6847936</t>
+          <t>6845667</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6884259</t>
+          <t>6882857</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2023</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>701</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>169</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15631</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>342</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>399116</t>
+          <t>399286</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297569</t>
+          <t>296996</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313032</t>
+          <t>313031</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>696891</t>
+          <t>698773</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>712858</t>
+          <t>712845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>20951</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7296</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28027</t>
+          <t>28767</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399347</t>
+          <t>402596</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>419278</t>
+          <t>419537</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>501486</t>
+          <t>501015</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510913</t>
+          <t>510253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>907613</t>
+          <t>906873</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>928344</t>
+          <t>927422</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2804</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14772</t>
+          <t>14831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12796</t>
+          <t>13046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>8988</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23777</t>
+          <t>24080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>521566</t>
+          <t>521507</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533611</t>
+          <t>533534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>579206</t>
+          <t>578956</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>587958</t>
+          <t>588082</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1104563</t>
+          <t>1104260</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1119729</t>
+          <t>1119352</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>5606</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27358</t>
+          <t>27397</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>10694</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23580</t>
+          <t>23316</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43534</t>
+          <t>45019</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>860428</t>
+          <t>860389</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>882027</t>
+          <t>882180</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>689301</t>
+          <t>689565</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>701941</t>
+          <t>702187</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1557133</t>
+          <t>1555648</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1582152</t>
+          <t>1581341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12882</t>
+          <t>13614</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31675</t>
+          <t>32032</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>13811</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27081</t>
+          <t>27010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30764</t>
+          <t>30744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53293</t>
+          <t>54229</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>529559</t>
+          <t>529202</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>548352</t>
+          <t>547620</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>520824</t>
+          <t>520895</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>533830</t>
+          <t>534094</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1055846</t>
+          <t>1054910</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1078375</t>
+          <t>1078395</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19270</t>
+          <t>19129</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23424</t>
+          <t>24001</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>446147</t>
+          <t>429837</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34401</t>
+          <t>33754</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>567629</t>
+          <t>579951</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>59,39%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>348895</t>
+          <t>349036</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>360788</t>
+          <t>360633</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>162221</t>
+          <t>178531</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>584944</t>
+          <t>584367</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>408904</t>
+          <t>396582</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>942132</t>
+          <t>942779</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5668</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>16585</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>23592</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39864</t>
+          <t>39644</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32653</t>
+          <t>32763</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52494</t>
+          <t>51840</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>265955</t>
+          <t>266174</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277221</t>
+          <t>277091</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>385967</t>
+          <t>386187</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>402091</t>
+          <t>402239</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>656096</t>
+          <t>656750</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>675937</t>
+          <t>675827</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56418</t>
+          <t>58510</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>95588</t>
+          <t>99242</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>103513</t>
+          <t>103528</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>941132</t>
+          <t>935404</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>176341</t>
+          <t>177115</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1103892</t>
+          <t>1053611</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3364229</t>
+          <t>3360575</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3403399</t>
+          <t>3401307</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2771148</t>
+          <t>2776876</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3608767</t>
+          <t>3608752</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,7 +12234,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6068205</t>
+          <t>6118486</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6995756</t>
+          <t>6994982</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_senso_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_senso_R-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12447</t>
+          <t>12281</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15416</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>485856</t>
+          <t>485647</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>455042</t>
+          <t>455208</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>464788</t>
+          <t>465469</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>946137</t>
+          <t>946582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>957787</t>
+          <t>957853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13182</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>11361</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18620</t>
+          <t>19307</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>722307</t>
+          <t>723163</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>733608</t>
+          <t>733606</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>614671</t>
+          <t>614133</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>623609</t>
+          <t>623560</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1342362</t>
+          <t>1341675</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1355572</t>
+          <t>1355628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12920</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>21566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624855</t>
+          <t>625770</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>637640</t>
+          <t>637012</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>676824</t>
+          <t>676255</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>687566</t>
+          <t>686749</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1307806</t>
+          <t>1306846</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1322743</t>
+          <t>1322240</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>12772</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17770</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1812,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>16471</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>10335</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>26699</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>16471</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>9422</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>26498</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>506526</t>
+          <t>506375</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>517062</t>
+          <t>517064</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>497872</t>
+          <t>497873</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>510504</t>
+          <t>510587</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,42 +1930,42 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>99,02%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1018318</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1008090</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>1024454</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
           <t>99,0%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>970</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1018318</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1008291</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1025367</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,41%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>6988</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21273</t>
+          <t>21061</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>13486</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31532</t>
+          <t>33293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>365437</t>
+          <t>365649</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>379528</t>
+          <t>379722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>387730</t>
+          <t>388208</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>399805</t>
+          <t>399946</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>759164</t>
+          <t>757403</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>777644</t>
+          <t>777210</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21313</t>
+          <t>21330</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11923</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29102</t>
+          <t>28955</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>271270</t>
+          <t>271253</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>284640</t>
+          <t>285254</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>331861</t>
+          <t>331011</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>341038</t>
+          <t>341025</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>606415</t>
+          <t>606562</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>622986</t>
+          <t>623023</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11479</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23551</t>
+          <t>24523</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12050</t>
+          <t>12135</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30249</t>
+          <t>31483</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>198154</t>
+          <t>198404</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>208084</t>
+          <t>208115</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>310357</t>
+          <t>309385</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>326089</t>
+          <t>325977</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>513542</t>
+          <t>512308</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>531741</t>
+          <t>531656</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37661</t>
+          <t>37702</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66661</t>
+          <t>65606</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43136</t>
+          <t>43055</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72447</t>
+          <t>73542</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>87814</t>
+          <t>87785</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>127417</t>
+          <t>127834</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3209882</t>
+          <t>3210937</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3238882</t>
+          <t>3238841</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3306750</t>
+          <t>3305655</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3336061</t>
+          <t>3336142</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6528324</t>
+          <t>6527907</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6567927</t>
+          <t>6567956</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12549</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15183</t>
+          <t>15012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>441597</t>
+          <t>441691</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>452040</t>
+          <t>452021</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>423572</t>
+          <t>423521</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>869193</t>
+          <t>869364</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>880420</t>
+          <t>880504</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>10318</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24119</t>
+          <t>24670</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11190</t>
+          <t>11313</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30216</t>
+          <t>31150</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>677062</t>
+          <t>676769</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>685291</t>
+          <t>685303</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>586136</t>
+          <t>585585</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>602714</t>
+          <t>602635</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1267126</t>
+          <t>1266192</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1286152</t>
+          <t>1286029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16461</t>
+          <t>15805</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20300</t>
+          <t>21427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11395</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>29823</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>665402</t>
+          <t>666058</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678934</t>
+          <t>679225</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>690550</t>
+          <t>689423</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>704964</t>
+          <t>704904</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1361807</t>
+          <t>1362889</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1381317</t>
+          <t>1381979</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>7986</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26384</t>
+          <t>25460</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24428</t>
+          <t>25057</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19285</t>
+          <t>19706</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44461</t>
+          <t>44724</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>588233</t>
+          <t>589157</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>607105</t>
+          <t>606631</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>591771</t>
+          <t>591142</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>607966</t>
+          <t>607803</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1186355</t>
+          <t>1186092</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1211531</t>
+          <t>1211110</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15815</t>
+          <t>14942</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>19650</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>12561</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31121</t>
+          <t>30201</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>413614</t>
+          <t>414487</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>425359</t>
+          <t>425504</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>428088</t>
+          <t>428150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>441521</t>
+          <t>441725</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>846108</t>
+          <t>847028</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>864377</t>
+          <t>864668</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15078</t>
+          <t>14818</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19257</t>
+          <t>21014</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>27958</t>
+          <t>28332</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>294708</t>
+          <t>294968</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>307768</t>
+          <t>307816</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>334739</t>
+          <t>332982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>348239</t>
+          <t>348097</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>635824</t>
+          <t>635450</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>653727</t>
+          <t>653920</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5065</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>18486</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19793</t>
+          <t>20229</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>14198</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32584</t>
+          <t>32352</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>231790</t>
+          <t>231365</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244786</t>
+          <t>244692</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>369186</t>
+          <t>368750</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>382732</t>
+          <t>382877</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>606246</t>
+          <t>606478</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>625160</t>
+          <t>624632</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43454</t>
+          <t>42672</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>76525</t>
+          <t>75290</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62695</t>
+          <t>61273</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97628</t>
+          <t>96951</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>113441</t>
+          <t>112025</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>160581</t>
+          <t>162776</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3350254</t>
+          <t>3351489</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3383325</t>
+          <t>3384107</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3460681</t>
+          <t>3461358</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3495614</t>
+          <t>3497036</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6824507</t>
+          <t>6822312</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6871647</t>
+          <t>6873063</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>6713</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414581</t>
+          <t>413807</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>391283</t>
+          <t>391299</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>809372</t>
+          <t>808505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1708</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2901</t>
+          <t>2757</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13290</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>583716</t>
+          <t>582865</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>553672</t>
+          <t>553290</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>561891</t>
+          <t>561836</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1140750</t>
+          <t>1140384</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1151139</t>
+          <t>1151283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12585</t>
+          <t>12325</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10385</t>
+          <t>10347</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4865</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>18159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656512</t>
+          <t>656772</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667165</t>
+          <t>667190</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>651001</t>
+          <t>651039</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>659527</t>
+          <t>659539</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1312493</t>
+          <t>1312324</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1325595</t>
+          <t>1325618</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22658</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11025</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28819</t>
+          <t>28748</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>623390</t>
+          <t>624885</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639616</t>
+          <t>639465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>636208</t>
+          <t>635854</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>647042</t>
+          <t>646143</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1266306</t>
+          <t>1266377</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1284100</t>
+          <t>1284051</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14876</t>
+          <t>15082</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8103,7 +8103,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19081</t>
+          <t>21444</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463042</t>
+          <t>462836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>475979</t>
+          <t>475946</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>487621</t>
+          <t>487732</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>955686</t>
+          <t>953323</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>970661</t>
+          <t>970840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>947</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11375</t>
+          <t>13412</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18217</t>
+          <t>17249</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323968</t>
+          <t>322933</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>333381</t>
+          <t>333383</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>366387</t>
+          <t>364350</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>375727</t>
+          <t>375047</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>693875</t>
+          <t>694843</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>707312</t>
+          <t>707284</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9326</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22520</t>
+          <t>22560</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28244</t>
+          <t>27392</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>247672</t>
+          <t>246753</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>256190</t>
+          <t>256087</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>377649</t>
+          <t>377609</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>394162</t>
+          <t>394994</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>628923</t>
+          <t>629775</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>648167</t>
+          <t>648280</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22996</t>
+          <t>22904</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>50111</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,49 +9107,49 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>37722</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>26305</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>51035</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>37722</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>26546</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>51329</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>65</t>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>56035</t>
+          <t>54381</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>93225</t>
+          <t>90609</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3345542</t>
+          <t>3344239</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3371354</t>
+          <t>3371446</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,47 +9220,47 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99,33%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3506820</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3493507</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3518237</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>98,94%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
           <t>98,56%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3506820</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3493213</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3517996</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>98,94%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>98,55%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6845667</t>
+          <t>6848283</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6882857</t>
+          <t>6884511</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>20765</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>24057</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399826</t>
+          <t>406003</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>399286</t>
+          <t>397769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>308757</t>
+          <t>355189</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296996</t>
+          <t>341747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313031</t>
+          <t>360864</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>708584</t>
+          <t>761192</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>698773</t>
+          <t>746248</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>712845</t>
+          <t>767258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>13189</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>5208</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20951</t>
+          <t>28086</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>12911</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15323</t>
+          <t>19243</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>10289</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28767</t>
+          <t>36018</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>413053</t>
+          <t>463701</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402596</t>
+          <t>448804</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>419537</t>
+          <t>471682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>507264</t>
+          <t>495679</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>501015</t>
+          <t>488822</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>510253</t>
+          <t>499545</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>920317</t>
+          <t>959380</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>906873</t>
+          <t>942605</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>927422</t>
+          <t>968334</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7251</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14831</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7687</t>
+          <t>10052</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13046</t>
+          <t>16558</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14873</t>
+          <t>17303</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8988</t>
+          <t>10947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24080</t>
+          <t>26349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>529152</t>
+          <t>613586</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>521507</t>
+          <t>606103</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>533534</t>
+          <t>618141</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>584315</t>
+          <t>613141</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>578956</t>
+          <t>606635</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>588082</t>
+          <t>617440</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1113467</t>
+          <t>1226726</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1104260</t>
+          <t>1217680</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1119352</t>
+          <t>1233082</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15190</t>
+          <t>17913</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>10268</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27397</t>
+          <t>27970</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16683</t>
+          <t>18458</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>12356</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23316</t>
+          <t>26245</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>31873</t>
+          <t>36371</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>27177</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45019</t>
+          <t>48147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>872596</t>
+          <t>682704</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>860389</t>
+          <t>672647</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>882180</t>
+          <t>690349</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>696198</t>
+          <t>718428</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>689565</t>
+          <t>710641</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>702187</t>
+          <t>724530</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1568794</t>
+          <t>1401133</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1555648</t>
+          <t>1389357</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1581341</t>
+          <t>1410327</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,17 +11037,17 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>21259</t>
+          <t>23071</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>14305</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32032</t>
+          <t>34271</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19871</t>
+          <t>23532</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27010</t>
+          <t>31562</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>46603</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30744</t>
+          <t>35574</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54229</t>
+          <t>59134</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -11150,17 +11150,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>539975</t>
+          <t>586275</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>529202</t>
+          <t>575075</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>547620</t>
+          <t>595041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>528034</t>
+          <t>585323</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>520895</t>
+          <t>577293</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>534094</t>
+          <t>592071</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1068009</t>
+          <t>1171599</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1054910</t>
+          <t>1159068</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1078395</t>
+          <t>1182628</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12049</t>
+          <t>13754</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19129</t>
+          <t>21776</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>222866</t>
+          <t>20574</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24001</t>
+          <t>14292</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>429837</t>
+          <t>27541</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>234915</t>
+          <t>34328</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33754</t>
+          <t>26199</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>579951</t>
+          <t>43911</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>356116</t>
+          <t>393326</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>349036</t>
+          <t>385304</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>360633</t>
+          <t>398390</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>385502</t>
+          <t>418592</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>178531</t>
+          <t>411625</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>584367</t>
+          <t>424874</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>741618</t>
+          <t>811918</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>396582</t>
+          <t>802335</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>942779</t>
+          <t>820047</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10417</t>
+          <t>11036</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16585</t>
+          <t>18093</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>31075</t>
+          <t>34693</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23592</t>
+          <t>27178</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39644</t>
+          <t>44764</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>41491</t>
+          <t>45729</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32763</t>
+          <t>36126</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>57941</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>272342</t>
+          <t>299162</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>266174</t>
+          <t>292105</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277091</t>
+          <t>303835</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>394756</t>
+          <t>429916</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>386187</t>
+          <t>419845</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>402239</t>
+          <t>437431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>667099</t>
+          <t>729078</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>656750</t>
+          <t>716866</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>675827</t>
+          <t>738681</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,102 +12066,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>76755</t>
+          <t>88005</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>58510</t>
+          <t>69106</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>99242</t>
+          <t>110224</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>120685</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>102653</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>141561</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>2,75%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>208690</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>185026</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>238607</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>2,87%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>307454</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>103528</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>935404</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>25,2%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>384209</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>177115</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>1053611</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -12179,102 +12179,102 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3383062</t>
+          <t>3444757</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3360575</t>
+          <t>3422538</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3401307</t>
+          <t>3463656</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>98,04%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>5185</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3616269</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3595393</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3634301</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>96,77%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>96,21%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>97,25%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>8475</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>7061026</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>7031109</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>7084690</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
           <t>97,13%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>98,31%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>5185</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3404826</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>2776876</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3608752</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>91,72%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>74,8%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>97,21%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>8475</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>6787888</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>6118486</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6994982</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>94,64%</t>
-        </is>
-      </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_senso_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P2A_senso_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad sensorial en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad sensorial en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
